--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -907,11 +907,11 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>300</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
         <v>4</v>
       </c>
       <c r="J16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.594594594594</v>
+        <v>-94.936708860759</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,13 +978,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="E17" s="15">
-        <v>-66.666666666666</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
         <v>5</v>
@@ -996,63 +996,63 @@
         <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J17" s="14">
         <v>7</v>
       </c>
       <c r="K17" s="15">
-        <v>42.857142857142</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L17" s="15">
-        <v>-28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
         <v>5</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-80</v>
-      </c>
-      <c r="F18" s="14">
-        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
         <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-46.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.700787401574</v>
+        <v>-94.520547945205</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,72 +1060,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>22.222222222222</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>23.684210526315</v>
+        <v>5.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J19" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K19" s="15">
-        <v>13.207547169811</v>
+        <v>8.196721311475</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.808219178082</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M19" s="15">
-        <v>-16.666666666666</v>
+        <v>-22.352941176470</v>
       </c>
       <c r="N19" s="15">
-        <v>-71.291866028708</v>
+        <v>-72.151898734177</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
         <v>33.333333333333</v>
@@ -1134,7 +1134,7 @@
         <v>21</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.939393939393</v>
+        <v>-95.180722891566</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,54 +1142,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.882352941176</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>17.543859649122</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="I21" s="17">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J21" s="17">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K21" s="18">
-        <v>7.407407407407</v>
+        <v>2.150537634408</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.909090909090</v>
+        <v>-22.764227642276</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.533980582524</v>
+        <v>-22.131147540983</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.634730538922</v>
+        <v>-83.391608391608</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
@@ -1201,19 +1201,19 @@
         <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>50</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F24" s="14">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H24" s="15">
-        <v>-35.632183908046</v>
+        <v>-29.487179487179</v>
       </c>
       <c r="I24" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J24" s="14">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.203389830508</v>
+        <v>-33.576642335766</v>
       </c>
       <c r="L24" s="15">
-        <v>-20</v>
+        <v>-22.881355932203</v>
       </c>
       <c r="M24" s="15">
-        <v>19.402985074626</v>
+        <v>15.189873417721</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>10</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F25" s="14">
         <v>42</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.235294117647</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J25" s="14">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.818181818181</v>
+        <v>-33.962264150943</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.052631578947</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
+        <v>15</v>
+      </c>
+      <c r="G26" s="14">
+        <v>8</v>
+      </c>
+      <c r="H26" s="15">
+        <v>87.5</v>
+      </c>
+      <c r="I26" s="14">
+        <v>19</v>
+      </c>
+      <c r="J26" s="14">
         <v>12</v>
       </c>
-      <c r="G26" s="14">
-        <v>7</v>
-      </c>
-      <c r="H26" s="15">
-        <v>71.428571428571</v>
-      </c>
-      <c r="I26" s="14">
-        <v>16</v>
-      </c>
-      <c r="J26" s="14">
-        <v>11</v>
-      </c>
       <c r="K26" s="15">
-        <v>45.454545454545</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>-36</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M26" s="15">
-        <v>-40.740740740740</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1399,11 +1399,11 @@
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
@@ -1431,29 +1431,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
       </c>
       <c r="J28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
         <v>-60</v>
@@ -1560,26 +1560,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1613,20 +1613,20 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -949,28 +949,28 @@
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
         <v>4</v>
       </c>
       <c r="J16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.857142857142</v>
+        <v>-60</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.555555555555</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.936708860759</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,7 +978,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -987,72 +987,72 @@
         <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14">
         <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J17" s="14">
         <v>7</v>
       </c>
       <c r="K17" s="15">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L17" s="15">
-        <v>-20</v>
+        <v>-18.75</v>
       </c>
       <c r="M17" s="15">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N17" s="15">
-        <v>-50</v>
+        <v>-55.172413793103</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
+        <v>10</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-70</v>
+      </c>
+      <c r="I18" s="14">
         <v>9</v>
       </c>
-      <c r="H18" s="15">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="I18" s="14">
-        <v>8</v>
-      </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M18" s="15">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.520547945205</v>
+        <v>-94.512195121951</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
         <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>-62.5</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>5.714285714285</v>
+        <v>-6.25</v>
       </c>
       <c r="I19" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K19" s="15">
-        <v>8.196721311475</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.428571428571</v>
+        <v>-28.125</v>
       </c>
       <c r="M19" s="15">
-        <v>-22.352941176470</v>
+        <v>-25</v>
       </c>
       <c r="N19" s="15">
-        <v>-72.151898734177</v>
+        <v>-74.538745387453</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="M20" s="15">
+        <v>400</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.180722891566</v>
+        <v>-94.680851063829</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
         <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.272727272727</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I21" s="17">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J21" s="17">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="K21" s="18">
-        <v>2.150537634408</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.764227642276</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.131147540983</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.391608391608</v>
+        <v>-84.283513097072</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1195,10 +1195,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1210,10 +1210,10 @@
         <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>-16.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-26.315789473684</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F24" s="14">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.487179487179</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="I24" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J24" s="14">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.576642335766</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.881355932203</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M24" s="15">
-        <v>15.189873417721</v>
+        <v>13.636363636363</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-44.444444444444</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F25" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.363636363636</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I25" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J25" s="14">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.962264150943</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.913043478260</v>
+        <v>-30.973451327433</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
         <v>1</v>
       </c>
       <c r="E26" s="15">
+        <v>300</v>
+      </c>
+      <c r="F26" s="14">
+        <v>18</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="15">
         <v>200</v>
       </c>
-      <c r="F26" s="14">
-        <v>15</v>
-      </c>
-      <c r="G26" s="14">
-        <v>8</v>
-      </c>
-      <c r="H26" s="15">
-        <v>87.5</v>
-      </c>
       <c r="I26" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="15">
-        <v>58.333333333333</v>
+        <v>76.923076923076</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.923076923076</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M26" s="15">
-        <v>-44.117647058823</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I16" s="14">
         <v>5</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-60</v>
-      </c>
-      <c r="I16" s="14">
-        <v>4</v>
       </c>
       <c r="J16" s="14">
         <v>6</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-60</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.454545454545</v>
+        <v>-94.949494949494</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="15">
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
+        <v>100</v>
+      </c>
+      <c r="I17" s="14">
+        <v>17</v>
+      </c>
+      <c r="J17" s="14">
+        <v>8</v>
+      </c>
+      <c r="K17" s="15">
+        <v>112.5</v>
+      </c>
+      <c r="L17" s="15">
         <v>0</v>
       </c>
-      <c r="I17" s="14">
-        <v>13</v>
-      </c>
-      <c r="J17" s="14">
-        <v>7</v>
-      </c>
-      <c r="K17" s="15">
-        <v>85.714285714285</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-18.75</v>
-      </c>
       <c r="M17" s="15">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="N17" s="15">
-        <v>-55.172413793103</v>
+        <v>-43.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-72.727272727272</v>
+      </c>
+      <c r="I18" s="14">
         <v>10</v>
       </c>
-      <c r="H18" s="15">
-        <v>-70</v>
-      </c>
-      <c r="I18" s="14">
-        <v>9</v>
-      </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.631578947368</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.769230769230</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.142857142857</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.512195121951</v>
+        <v>-94.652406417112</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-62.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.25</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J19" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>3.846153846153</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.125</v>
+        <v>-24.299065420560</v>
       </c>
       <c r="M19" s="15">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="N19" s="15">
-        <v>-74.538745387453</v>
+        <v>-72.542372881355</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1122,19 +1122,19 @@
         <v>5</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
         <v>25</v>
       </c>
       <c r="M20" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.680851063829</v>
+        <v>-95.370370370370</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
         <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.153846153846</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
         <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.181818181818</v>
+        <v>-10.909090909090</v>
       </c>
       <c r="I21" s="17">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="J21" s="17">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.773584905660</v>
+        <v>0.840336134453</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.169014084507</v>
+        <v>-25</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.444444444444</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.283513097072</v>
+        <v>-83.379501385041</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1195,10 +1195,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1210,10 +1210,10 @@
         <v>25</v>
       </c>
       <c r="L22" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="M22" s="15">
         <v>-37.5</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.076923076923</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G24" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.949152542372</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="J24" s="14">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.864197530864</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.571428571428</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="M24" s="15">
-        <v>13.636363636363</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-27.272727272727</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.529411764705</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="I25" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J25" s="14">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.973451327433</v>
+        <v>-29.133858267716</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
         <v>6</v>
       </c>
       <c r="H26" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K26" s="15">
-        <v>76.923076923076</v>
+        <v>80</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.689655172413</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M26" s="15">
-        <v>-36.111111111111</v>
+        <v>-32.5</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -914,45 +914,45 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
         <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <v>2</v>
       </c>
       <c r="G16" s="14">
         <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
@@ -964,13 +964,13 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L16" s="15">
+        <v>-61.538461538461</v>
+      </c>
+      <c r="M16" s="15">
         <v>-58.333333333333</v>
       </c>
-      <c r="M16" s="15">
-        <v>-54.545454545454</v>
-      </c>
       <c r="N16" s="15">
-        <v>-94.949494949494</v>
+        <v>-95.370370370370</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="15">
-        <v>100</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J17" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K17" s="15">
-        <v>112.5</v>
+        <v>90</v>
       </c>
       <c r="L17" s="15">
         <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.333333333333</v>
+        <v>-40.625</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>4</v>
+      </c>
+      <c r="G18" s="14">
+        <v>8</v>
+      </c>
+      <c r="H18" s="15">
         <v>-50</v>
       </c>
-      <c r="F18" s="14">
-        <v>3</v>
-      </c>
-      <c r="G18" s="14">
-        <v>11</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-72.727272727272</v>
-      </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.176470588235</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.652406417112</v>
+        <v>-94.230769230769</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.882352941176</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I19" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J19" s="14">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K19" s="15">
-        <v>3.846153846153</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.299065420560</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M19" s="15">
-        <v>-19</v>
+        <v>-22.881355932203</v>
       </c>
       <c r="N19" s="15">
-        <v>-72.542372881355</v>
+        <v>-72.672672672672</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1119,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
+        <v>20</v>
+      </c>
+      <c r="L20" s="15">
         <v>0</v>
       </c>
-      <c r="L20" s="15">
-        <v>25</v>
-      </c>
       <c r="M20" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.370370370370</v>
+        <v>-95.041322314049</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,13 +1142,13 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>38.461538461538</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
         <v>49</v>
@@ -1160,22 +1160,22 @@
         <v>-10.909090909090</v>
       </c>
       <c r="I21" s="17">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="J21" s="17">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="K21" s="18">
-        <v>0.840336134453</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-25</v>
+        <v>-23.595505617977</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.367346938775</v>
+        <v>-20</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.379501385041</v>
+        <v>-83.105590062111</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,14 +1191,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>3</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>200</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>-37.5</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>8.333333333333</v>
+        <v>-79.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.928571428571</v>
+        <v>-39.705882352941</v>
       </c>
       <c r="I24" s="14">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J24" s="14">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.864197530864</v>
+        <v>-36.559139784946</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.205128205128</v>
+        <v>-35.164835164835</v>
       </c>
       <c r="M24" s="15">
-        <v>16.666666666666</v>
+        <v>4.424778761061</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>71.428571428571</v>
+        <v>-68.75</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H25" s="15">
-        <v>-10.869565217391</v>
+        <v>-32.692307692307</v>
       </c>
       <c r="I25" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J25" s="14">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.419354838709</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.133858267716</v>
+        <v>-37.086092715231</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" s="15">
-        <v>233.333333333333</v>
+        <v>157.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J26" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K26" s="15">
-        <v>80</v>
+        <v>88.888888888888</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.857142857142</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="M26" s="15">
-        <v>-32.5</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1570,16 +1570,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
+        <v>50</v>
+      </c>
+      <c r="L31" s="15">
         <v>0</v>
-      </c>
-      <c r="L31" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -567,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -881,8 +881,8 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -895,40 +895,40 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="15">
+        <v>3</v>
+      </c>
+      <c r="J15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="14">
-        <v>3</v>
-      </c>
-      <c r="J15" s="14">
-        <v>1</v>
-      </c>
-      <c r="K15" s="15">
+      <c r="K15" s="14">
         <v>200</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="14">
         <v>-25</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="14">
         <v>0</v>
       </c>
     </row>
@@ -936,8 +936,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -945,162 +945,162 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-75</v>
-      </c>
-      <c r="I16" s="14">
-        <v>5</v>
-      </c>
-      <c r="J16" s="14">
+      <c r="F16" s="15">
+        <v>3</v>
+      </c>
+      <c r="G16" s="15">
+        <v>2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>50</v>
+      </c>
+      <c r="I16" s="15">
+        <v>7</v>
+      </c>
+      <c r="J16" s="15">
         <v>6</v>
       </c>
-      <c r="K16" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="L16" s="15">
-        <v>-61.538461538461</v>
-      </c>
-      <c r="M16" s="15">
-        <v>-58.333333333333</v>
-      </c>
-      <c r="N16" s="15">
-        <v>-95.370370370370</v>
+      <c r="K16" s="14">
+        <v>16.666666666666</v>
+      </c>
+      <c r="L16" s="14">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="M16" s="14">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="N16" s="14">
+        <v>-93.913043478260</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
-      <c r="E17" s="15">
-        <v>0</v>
-      </c>
-      <c r="F17" s="14">
-        <v>10</v>
-      </c>
-      <c r="G17" s="14">
-        <v>3</v>
-      </c>
-      <c r="H17" s="15">
-        <v>233.333333333333</v>
-      </c>
-      <c r="I17" s="14">
-        <v>19</v>
-      </c>
-      <c r="J17" s="14">
-        <v>10</v>
-      </c>
-      <c r="K17" s="15">
-        <v>90</v>
-      </c>
-      <c r="L17" s="15">
-        <v>0</v>
-      </c>
-      <c r="M17" s="15">
-        <v>90</v>
-      </c>
-      <c r="N17" s="15">
-        <v>-40.625</v>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="15">
+        <v>9</v>
+      </c>
+      <c r="G17" s="15">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>80</v>
+      </c>
+      <c r="I17" s="15">
+        <v>21</v>
+      </c>
+      <c r="J17" s="15">
+        <v>12</v>
+      </c>
+      <c r="K17" s="14">
+        <v>75</v>
+      </c>
+      <c r="L17" s="14">
+        <v>5</v>
+      </c>
+      <c r="M17" s="14">
+        <v>75</v>
+      </c>
+      <c r="N17" s="14">
+        <v>-40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>4</v>
-      </c>
-      <c r="G18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="15">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15">
         <v>8</v>
       </c>
-      <c r="H18" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I18" s="14">
-        <v>12</v>
-      </c>
-      <c r="J18" s="14">
-        <v>23</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-47.826086956521</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-36.842105263157</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="N18" s="15">
-        <v>-94.230769230769</v>
+      <c r="H18" s="14">
+        <v>-62.5</v>
+      </c>
+      <c r="I18" s="15">
+        <v>11</v>
+      </c>
+      <c r="J18" s="15">
+        <v>24</v>
+      </c>
+      <c r="K18" s="14">
+        <v>-54.166666666666</v>
+      </c>
+      <c r="L18" s="14">
+        <v>-42.105263157894</v>
+      </c>
+      <c r="M18" s="14">
+        <v>-64.516129032258</v>
+      </c>
+      <c r="N18" s="14">
+        <v>-95.397489539749</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
-        <v>11</v>
-      </c>
-      <c r="D19" s="14">
-        <v>13</v>
-      </c>
-      <c r="E19" s="15">
-        <v>-15.384615384615</v>
-      </c>
-      <c r="F19" s="14">
-        <v>30</v>
-      </c>
-      <c r="G19" s="14">
-        <v>38</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-21.052631578947</v>
-      </c>
-      <c r="I19" s="14">
-        <v>91</v>
-      </c>
-      <c r="J19" s="14">
-        <v>91</v>
-      </c>
-      <c r="K19" s="15">
-        <v>0</v>
-      </c>
-      <c r="L19" s="15">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-22.881355932203</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-72.672672672672</v>
+      <c r="C19" s="15">
+        <v>10</v>
+      </c>
+      <c r="D19" s="15">
+        <v>6</v>
+      </c>
+      <c r="E19" s="14">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F19" s="15">
+        <v>35</v>
+      </c>
+      <c r="G19" s="15">
+        <v>36</v>
+      </c>
+      <c r="H19" s="14">
+        <v>-2.777777777777</v>
+      </c>
+      <c r="I19" s="15">
+        <v>101</v>
+      </c>
+      <c r="J19" s="15">
+        <v>97</v>
+      </c>
+      <c r="K19" s="14">
+        <v>4.123711340206</v>
+      </c>
+      <c r="L19" s="14">
+        <v>-25.185185185185</v>
+      </c>
+      <c r="M19" s="14">
+        <v>-25.185185185185</v>
+      </c>
+      <c r="N19" s="14">
+        <v>-73.629242819843</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="15">
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
@@ -1109,32 +1109,32 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
-        <v>2</v>
-      </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
-      <c r="H20" s="15">
+      <c r="F20" s="15">
+        <v>3</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
+        <v>7</v>
+      </c>
+      <c r="J20" s="15">
+        <v>5</v>
+      </c>
+      <c r="K20" s="14">
+        <v>40</v>
+      </c>
+      <c r="L20" s="14">
         <v>0</v>
       </c>
-      <c r="I20" s="14">
-        <v>6</v>
-      </c>
-      <c r="J20" s="14">
-        <v>5</v>
-      </c>
-      <c r="K20" s="15">
-        <v>20</v>
-      </c>
-      <c r="L20" s="15">
-        <v>0</v>
-      </c>
-      <c r="M20" s="15">
-        <v>200</v>
-      </c>
-      <c r="N20" s="15">
-        <v>-95.041322314049</v>
+      <c r="M20" s="14">
+        <v>250</v>
+      </c>
+      <c r="N20" s="14">
+        <v>-94.696969696969</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.909090909090</v>
+        <v>5.769230769230</v>
       </c>
       <c r="I21" s="17">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="J21" s="17">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>3.448275862068</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.595505617977</v>
+        <v>-24.623115577889</v>
       </c>
       <c r="M21" s="18">
-        <v>-20</v>
+        <v>-22.279792746114</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.105590062111</v>
+        <v>-83.461962513781</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,8 +1191,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="15">
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1200,20 +1200,20 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="14">
-        <v>5</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="I22" s="15">
+        <v>8</v>
+      </c>
+      <c r="J22" s="15">
         <v>4</v>
       </c>
-      <c r="K22" s="15">
-        <v>25</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-37.5</v>
+      <c r="K22" s="14">
+        <v>100</v>
+      </c>
+      <c r="L22" s="14">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="M22" s="14">
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1264,38 +1264,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="14">
-        <v>5</v>
-      </c>
-      <c r="D24" s="14">
-        <v>24</v>
-      </c>
-      <c r="E24" s="15">
-        <v>-79.166666666666</v>
-      </c>
-      <c r="F24" s="14">
-        <v>41</v>
-      </c>
-      <c r="G24" s="14">
-        <v>68</v>
-      </c>
-      <c r="H24" s="15">
-        <v>-39.705882352941</v>
-      </c>
-      <c r="I24" s="14">
-        <v>118</v>
-      </c>
-      <c r="J24" s="14">
-        <v>186</v>
-      </c>
-      <c r="K24" s="15">
-        <v>-36.559139784946</v>
-      </c>
-      <c r="L24" s="15">
-        <v>-35.164835164835</v>
-      </c>
-      <c r="M24" s="15">
-        <v>4.424778761061</v>
+      <c r="C24" s="15">
+        <v>12</v>
+      </c>
+      <c r="D24" s="15">
+        <v>12</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15">
+        <v>40</v>
+      </c>
+      <c r="G24" s="15">
+        <v>61</v>
+      </c>
+      <c r="H24" s="14">
+        <v>-34.426229508196</v>
+      </c>
+      <c r="I24" s="15">
+        <v>130</v>
+      </c>
+      <c r="J24" s="15">
+        <v>198</v>
+      </c>
+      <c r="K24" s="14">
+        <v>-34.343434343434</v>
+      </c>
+      <c r="L24" s="14">
+        <v>-35.323383084577</v>
+      </c>
+      <c r="M24" s="14">
+        <v>2.362204724409</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,35 +1305,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>5</v>
-      </c>
-      <c r="D25" s="14">
-        <v>16</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-68.75</v>
-      </c>
-      <c r="F25" s="14">
-        <v>35</v>
-      </c>
-      <c r="G25" s="14">
-        <v>52</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-32.692307692307</v>
-      </c>
-      <c r="I25" s="14">
-        <v>95</v>
-      </c>
-      <c r="J25" s="14">
-        <v>140</v>
-      </c>
-      <c r="K25" s="15">
-        <v>-32.142857142857</v>
-      </c>
-      <c r="L25" s="15">
-        <v>-37.086092715231</v>
+      <c r="C25" s="15">
+        <v>6</v>
+      </c>
+      <c r="D25" s="15">
+        <v>8</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-25</v>
+      </c>
+      <c r="F25" s="15">
+        <v>31</v>
+      </c>
+      <c r="G25" s="15">
+        <v>42</v>
+      </c>
+      <c r="H25" s="14">
+        <v>-26.190476190476</v>
+      </c>
+      <c r="I25" s="15">
+        <v>101</v>
+      </c>
+      <c r="J25" s="15">
+        <v>148</v>
+      </c>
+      <c r="K25" s="14">
+        <v>-31.756756756756</v>
+      </c>
+      <c r="L25" s="14">
+        <v>-39.880952380952</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>7</v>
-      </c>
-      <c r="D26" s="14">
+      <c r="C26" s="15">
         <v>3</v>
       </c>
-      <c r="E26" s="15">
-        <v>133.333333333333</v>
-      </c>
-      <c r="F26" s="14">
-        <v>18</v>
-      </c>
-      <c r="G26" s="14">
-        <v>7</v>
-      </c>
-      <c r="H26" s="15">
-        <v>157.142857142857</v>
-      </c>
-      <c r="I26" s="14">
-        <v>34</v>
-      </c>
-      <c r="J26" s="14">
-        <v>18</v>
-      </c>
-      <c r="K26" s="15">
-        <v>88.888888888888</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-12.820512820512</v>
-      </c>
-      <c r="M26" s="15">
-        <v>-22.727272727272</v>
+      <c r="D26" s="15">
+        <v>4</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-25</v>
+      </c>
+      <c r="F26" s="15">
+        <v>19</v>
+      </c>
+      <c r="G26" s="15">
+        <v>10</v>
+      </c>
+      <c r="H26" s="14">
+        <v>90</v>
+      </c>
+      <c r="I26" s="15">
+        <v>38</v>
+      </c>
+      <c r="J26" s="15">
+        <v>22</v>
+      </c>
+      <c r="K26" s="14">
+        <v>72.727272727272</v>
+      </c>
+      <c r="L26" s="14">
+        <v>-7.317073170731</v>
+      </c>
+      <c r="M26" s="14">
+        <v>-26.923076923076</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,34 +1387,34 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="15">
+        <v>3</v>
+      </c>
+      <c r="J27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="14">
-        <v>3</v>
-      </c>
-      <c r="J27" s="14">
-        <v>1</v>
-      </c>
-      <c r="K27" s="15">
+      <c r="K27" s="14">
         <v>200</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="14">
         <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="C28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>8</v>
+      </c>
+      <c r="G28" s="15">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>166.666666666667</v>
+      </c>
+      <c r="I28" s="15">
+        <v>10</v>
+      </c>
+      <c r="J28" s="15">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>25</v>
-      </c>
-      <c r="I28" s="14">
-        <v>7</v>
-      </c>
-      <c r="J28" s="14">
-        <v>5</v>
-      </c>
-      <c r="K28" s="15">
-        <v>40</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-22.222222222222</v>
+      <c r="K28" s="14">
+        <v>100</v>
+      </c>
+      <c r="L28" s="14">
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,34 +1551,34 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
-      </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="15">
         <v>3</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="15">
         <v>2</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="14">
         <v>50</v>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="14">
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1628,13 +1628,13 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="15">
         <v>1</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="15">
         <v>1</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="14">
         <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
@@ -1745,16 +1745,16 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>6</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="15">
         <v>0</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <v>0</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="15">
         <v>0</v>
       </c>
       <c r="K39" s="13" t="s">
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>12</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="15">
         <v>14</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="15">
         <v>7</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="15">
         <v>8</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="15">
         <v>14</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="14">
         <v>75</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="14">
         <v>100</v>
       </c>
-      <c r="M40" s="15">
+      <c r="M40" s="14">
         <v>0</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="14">
         <v>16.666666666666</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>740</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="15">
         <v>619</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <v>247</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="15">
         <v>149</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="15">
         <v>59</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="14">
         <v>-60.402684563758</v>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="14">
         <v>-76.113360323886</v>
       </c>
-      <c r="M41" s="15">
+      <c r="M41" s="14">
         <v>-90.468497576736</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="14">
         <v>-92.027027027027</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="15">
         <v>181</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="15">
         <v>161</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <v>79</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="15">
         <v>103</v>
       </c>
-      <c r="J42" s="14">
+      <c r="J42" s="15">
         <v>94</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="14">
         <v>-8.737864077669</v>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="14">
         <v>18.987341772151</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="14">
         <v>-41.614906832298</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="14">
         <v>-48.066298342541</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="15">
         <v>1412</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="15">
         <v>1230</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <v>548</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="15">
         <v>265</v>
       </c>
-      <c r="J43" s="14">
+      <c r="J43" s="15">
         <v>102</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="14">
         <v>-61.509433962264</v>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="14">
         <v>-81.386861313868</v>
       </c>
-      <c r="M43" s="15">
+      <c r="M43" s="14">
         <v>-91.707317073170</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="14">
         <v>-92.776203966005</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="15">
         <v>2910</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="15">
         <v>2287</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <v>1490</v>
       </c>
-      <c r="I44" s="14">
+      <c r="I44" s="15">
         <v>1312</v>
       </c>
-      <c r="J44" s="14">
+      <c r="J44" s="15">
         <v>559</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="14">
         <v>-57.393292682926</v>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="14">
         <v>-62.483221476510</v>
       </c>
-      <c r="M44" s="15">
+      <c r="M44" s="14">
         <v>-75.557498906864</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="14">
         <v>-80.790378006872</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="15">
         <v>843</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="15">
         <v>639</v>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <v>203</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="15">
         <v>111</v>
       </c>
-      <c r="J45" s="14">
+      <c r="J45" s="15">
         <v>28</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="14">
         <v>-74.774774774774</v>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="14">
         <v>-86.206896551724</v>
       </c>
-      <c r="M45" s="15">
+      <c r="M45" s="14">
         <v>-95.618153364632</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="14">
         <v>-96.678529062870</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -925,8 +925,8 @@
       <c r="L15" s="14">
         <v>-25</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="14">
+        <v>200</v>
       </c>
       <c r="N15" s="14">
         <v>0</v>
@@ -936,82 +936,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I16" s="15">
         <v>7</v>
       </c>
       <c r="J16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
         <v>-46.153846153846</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.913043478260</v>
+        <v>-94.573643410852</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>3</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>80</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="15">
         <v>21</v>
       </c>
       <c r="J17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K17" s="14">
-        <v>75</v>
+        <v>61.538461538461</v>
       </c>
       <c r="L17" s="14">
-        <v>5</v>
+        <v>-12.5</v>
       </c>
       <c r="M17" s="14">
         <v>75</v>
       </c>
       <c r="N17" s="14">
-        <v>-40</v>
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-62.5</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I18" s="15">
         <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K18" s="14">
-        <v>-54.166666666666</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="L18" s="14">
-        <v>-42.105263157894</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="14">
-        <v>-64.516129032258</v>
+        <v>-65.625</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.397489539749</v>
+        <v>-95.785440613026</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>66.666666666666</v>
+        <v>62.5</v>
       </c>
       <c r="F19" s="15">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G19" s="15">
         <v>36</v>
       </c>
       <c r="H19" s="14">
-        <v>-2.777777777777</v>
+        <v>25</v>
       </c>
       <c r="I19" s="15">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J19" s="15">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K19" s="14">
-        <v>4.123711340206</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L19" s="14">
-        <v>-25.185185185185</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="M19" s="14">
-        <v>-25.185185185185</v>
+        <v>-24</v>
       </c>
       <c r="N19" s="14">
-        <v>-73.629242819843</v>
+        <v>-72.330097087378</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1119,22 +1119,22 @@
         <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M20" s="14">
-        <v>250</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.696969696969</v>
+        <v>-94.482758620689</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>77.777777777777</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" s="18">
-        <v>5.769230769230</v>
+        <v>21.568627450980</v>
       </c>
       <c r="I21" s="17">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J21" s="17">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="K21" s="18">
-        <v>3.448275862068</v>
+        <v>4.458598726114</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.623115577889</v>
+        <v>-24.423963133640</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.279792746114</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.461962513781</v>
+        <v>-83.417593528817</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>3</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,10 +1210,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="14">
-        <v>-38.461538461538</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1268,34 +1268,34 @@
         <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G24" s="15">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.426229508196</v>
+        <v>-34.920634920634</v>
       </c>
       <c r="I24" s="15">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J24" s="15">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="K24" s="14">
-        <v>-34.343434343434</v>
+        <v>-33.802816901408</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.323383084577</v>
+        <v>-34.722222222222</v>
       </c>
       <c r="M24" s="14">
-        <v>2.362204724409</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F25" s="15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" s="15">
         <v>42</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.190476190476</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="15">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J25" s="15">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.756756756756</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.880952380952</v>
+        <v>-39.664804469273</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>90</v>
+        <v>31.25</v>
       </c>
       <c r="I26" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J26" s="15">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K26" s="14">
-        <v>72.727272727272</v>
+        <v>51.724137931034</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.317073170731</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="M26" s="14">
-        <v>-26.923076923076</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,19 +914,19 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
         <v>1</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L15" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="14">
         <v>0</v>
@@ -936,82 +936,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>1</v>
       </c>
       <c r="H16" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J16" s="15">
         <v>7</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>-46.153846153846</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.573643410852</v>
+        <v>-93.793103448275</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="15">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-100</v>
+      <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
         <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>33.333333333333</v>
+        <v>60</v>
       </c>
       <c r="I17" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J17" s="15">
         <v>13</v>
       </c>
       <c r="K17" s="14">
-        <v>61.538461538461</v>
+        <v>100</v>
       </c>
       <c r="L17" s="14">
-        <v>-12.5</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M17" s="14">
-        <v>75</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N17" s="14">
-        <v>-46.153846153846</v>
+        <v>-38.095238095238</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>-71.428571428571</v>
+        <v>-87.5</v>
       </c>
       <c r="I18" s="15">
         <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K18" s="14">
-        <v>-57.692307692307</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="L18" s="14">
-        <v>-50</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="M18" s="14">
-        <v>-65.625</v>
+        <v>-69.444444444444</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.785440613026</v>
+        <v>-96.113074204947</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
         <v>45</v>
       </c>
       <c r="G19" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I19" s="15">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J19" s="15">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K19" s="14">
-        <v>8.571428571428</v>
+        <v>10.619469026548</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.917808219178</v>
+        <v>-17.763157894736</v>
       </c>
       <c r="M19" s="14">
-        <v>-24</v>
+        <v>-23.780487804878</v>
       </c>
       <c r="N19" s="14">
-        <v>-72.330097087378</v>
+        <v>-72.406181015452</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,31 +1110,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="14">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L20" s="14">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M20" s="14">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.482758620689</v>
+        <v>-94.230769230769</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>63.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H21" s="18">
-        <v>21.568627450980</v>
+        <v>30.612244897959</v>
       </c>
       <c r="I21" s="17">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="J21" s="17">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="K21" s="18">
-        <v>4.458598726114</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.423963133640</v>
+        <v>-19.650655021834</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.641509433962</v>
+        <v>-21.367521367521</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.417593528817</v>
+        <v>-83.010156971375</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="14">
-        <v>-20</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F24" s="15">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" s="15">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.920634920634</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I24" s="15">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J24" s="15">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.802816901408</v>
+        <v>-33.478260869565</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.722222222222</v>
+        <v>-35.443037974683</v>
       </c>
       <c r="M24" s="14">
-        <v>-4.081632653061</v>
+        <v>-3.164556962025</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" s="14">
-        <v>-36.363636363636</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F25" s="15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G25" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H25" s="14">
-        <v>-28.571428571428</v>
+        <v>-47.916666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J25" s="15">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K25" s="14">
-        <v>-32.075471698113</v>
+        <v>-33.139534883720</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.664804469273</v>
+        <v>-41.326530612244</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15">
         <v>6</v>
       </c>
-      <c r="D26" s="15">
-        <v>7</v>
-      </c>
       <c r="E26" s="14">
-        <v>-14.285714285714</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>31.25</v>
+        <v>-15</v>
       </c>
       <c r="I26" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J26" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K26" s="14">
-        <v>51.724137931034</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.204081632653</v>
+        <v>-20.370370370370</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.518518518518</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L27" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="15">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1629,13 +1629,13 @@
         <v>21</v>
       </c>
       <c r="I33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="15">
         <v>1</v>
       </c>
       <c r="K33" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,17 +895,17 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
         <v>0</v>
@@ -936,123 +936,123 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
+        <v>3</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
+        <v>3</v>
+      </c>
+      <c r="G16" s="15">
         <v>4</v>
       </c>
-      <c r="G16" s="15">
-        <v>1</v>
-      </c>
       <c r="H16" s="14">
-        <v>300</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J16" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16" s="14">
-        <v>28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-40</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.793103448275</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>3</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="15">
+        <v>2</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
         <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I17" s="15">
         <v>26</v>
       </c>
       <c r="J17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K17" s="14">
-        <v>100</v>
+        <v>73.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-3.703703703703</v>
+        <v>-18.75</v>
       </c>
       <c r="M17" s="14">
-        <v>85.714285714285</v>
+        <v>62.5</v>
       </c>
       <c r="N17" s="14">
-        <v>-38.095238095238</v>
+        <v>-40.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-87.5</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-62.068965517241</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-52.173913043478</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-69.444444444444</v>
+        <v>-64.864864864864</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.113074204947</v>
+        <v>-95.751633986928</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="14">
-        <v>28.571428571428</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J19" s="15">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="K19" s="14">
-        <v>10.619469026548</v>
+        <v>2.362204724409</v>
       </c>
       <c r="L19" s="14">
-        <v>-17.763157894736</v>
+        <v>-17.721518987341</v>
       </c>
       <c r="M19" s="14">
-        <v>-23.780487804878</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N19" s="14">
-        <v>-72.406181015452</v>
+        <v>-73.630831643002</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1119,22 +1119,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L20" s="14">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.230769230769</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>63.636363636363</v>
+        <v>-55</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G21" s="17">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>30.612244897959</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J21" s="17">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="K21" s="18">
-        <v>9.523809523809</v>
+        <v>1.595744680851</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.650655021834</v>
+        <v>-22.357723577235</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.367521367521</v>
+        <v>-21.721311475409</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.010156971375</v>
+        <v>-83.716965046888</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1201,19 +1201,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
         <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L22" s="14">
-        <v>-46.666666666666</v>
+        <v>-43.75</v>
       </c>
       <c r="M22" s="14">
-        <v>-27.272727272727</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-23.529411764705</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F24" s="15">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G24" s="15">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H24" s="14">
-        <v>-41.176470588235</v>
+        <v>-20</v>
       </c>
       <c r="I24" s="15">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="J24" s="15">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.478260869565</v>
+        <v>-32.270916334661</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.443037974683</v>
+        <v>-32.806324110671</v>
       </c>
       <c r="M24" s="14">
-        <v>-3.164556962025</v>
+        <v>1.190476190476</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
         <v>13</v>
       </c>
       <c r="E25" s="14">
-        <v>-46.153846153846</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F25" s="15">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G25" s="15">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.916666666666</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="I25" s="15">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J25" s="15">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="K25" s="14">
-        <v>-33.139534883720</v>
+        <v>-31.351351351351</v>
       </c>
       <c r="L25" s="14">
-        <v>-41.326530612244</v>
+        <v>-40.094339622641</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>1</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G26" s="15">
         <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>-15</v>
+        <v>-50</v>
       </c>
       <c r="I26" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K26" s="14">
-        <v>22.857142857142</v>
+        <v>15.789473684210</v>
       </c>
       <c r="L26" s="14">
-        <v>-20.370370370370</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>-23.214285714285</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-23.076923076923</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D31" s="15">
         <v>1</v>
       </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L31" s="14">
         <v>0</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,36 +914,36 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>1</v>
       </c>
       <c r="K15" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M15" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-100</v>
+      <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>3</v>
@@ -955,104 +955,104 @@
         <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16" s="15">
         <v>10</v>
       </c>
       <c r="K16" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.871794871794</v>
+        <v>-93.975903614457</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
         <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="14">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="I17" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" s="14">
-        <v>73.333333333333</v>
+        <v>81.25</v>
       </c>
       <c r="L17" s="14">
-        <v>-18.75</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M17" s="14">
-        <v>62.5</v>
+        <v>70.588235294117</v>
       </c>
       <c r="N17" s="14">
-        <v>-40.909090909090</v>
+        <v>-36.956521739130</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>2</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-71.428571428571</v>
+        <v>-80</v>
       </c>
       <c r="I18" s="15">
         <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K18" s="14">
-        <v>-56.666666666666</v>
+        <v>-61.764705882352</v>
       </c>
       <c r="L18" s="14">
-        <v>-53.571428571428</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="M18" s="14">
         <v>-64.864864864864</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.751633986928</v>
+        <v>-95.987654320987</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>11</v>
+      </c>
+      <c r="D19" s="15">
         <v>7</v>
       </c>
-      <c r="D19" s="15">
-        <v>14</v>
-      </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F19" s="15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G19" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>8.333333333333</v>
+        <v>10.810810810810</v>
       </c>
       <c r="I19" s="15">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J19" s="15">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K19" s="14">
-        <v>2.362204724409</v>
+        <v>5.223880597014</v>
       </c>
       <c r="L19" s="14">
-        <v>-17.721518987341</v>
+        <v>-15.568862275449</v>
       </c>
       <c r="M19" s="14">
-        <v>-23.529411764705</v>
+        <v>-22.099447513812</v>
       </c>
       <c r="N19" s="14">
-        <v>-73.630831643002</v>
+        <v>-73.040152963671</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1110,7 +1110,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1134,7 +1134,7 @@
         <v>233.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.117647058823</v>
+        <v>-94.475138121547</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,57 +1142,57 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-55</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>7.692307692307</v>
+        <v>5.454545454545</v>
       </c>
       <c r="I21" s="17">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="J21" s="17">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="K21" s="18">
-        <v>1.595744680851</v>
+        <v>4</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.357723577235</v>
+        <v>-20.912547528517</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.721311475409</v>
+        <v>-19.066147859922</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.716965046888</v>
+        <v>-83.279742765273</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>4</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>125</v>
       </c>
       <c r="L22" s="14">
-        <v>-43.75</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M22" s="14">
         <v>-25</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>-14.285714285714</v>
+        <v>-35</v>
       </c>
       <c r="F24" s="15">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G24" s="15">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H24" s="14">
-        <v>-20</v>
+        <v>-24.657534246575</v>
       </c>
       <c r="I24" s="15">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="J24" s="15">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.270916334661</v>
+        <v>-32.472324723247</v>
       </c>
       <c r="L24" s="14">
-        <v>-32.806324110671</v>
+        <v>-33.454545454545</v>
       </c>
       <c r="M24" s="14">
-        <v>1.190476190476</v>
+        <v>-0.543478260869</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E25" s="14">
-        <v>-7.692307692307</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F25" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G25" s="15">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H25" s="14">
-        <v>-28.888888888888</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I25" s="15">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="J25" s="15">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.351351351351</v>
+        <v>-31.862745098039</v>
       </c>
       <c r="L25" s="14">
-        <v>-40.094339622641</v>
+        <v>-40.086206896551</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H26" s="14">
-        <v>-50</v>
+        <v>-64</v>
       </c>
       <c r="I26" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J26" s="15">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K26" s="14">
-        <v>15.789473684210</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="L26" s="14">
-        <v>-26.666666666666</v>
+        <v>-28.125</v>
       </c>
       <c r="M26" s="14">
-        <v>-24.137931034482</v>
+        <v>-24.590163934426</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1432,31 +1432,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
       </c>
-      <c r="F28" s="15">
-        <v>3</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>66.666666666666</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L28" s="14">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1573,10 +1573,10 @@
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L31" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -936,14 +936,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>3</v>
@@ -958,19 +958,19 @@
         <v>10</v>
       </c>
       <c r="J16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L16" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
         <v>-37.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.975903614457</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
         <v>4</v>
       </c>
       <c r="H17" s="14">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="I17" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" s="14">
-        <v>81.25</v>
+        <v>94.117647058823</v>
       </c>
       <c r="L17" s="14">
-        <v>-17.142857142857</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="M17" s="14">
-        <v>70.588235294117</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-36.956521739130</v>
+        <v>-35.294117647058</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,7 +1022,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
@@ -1031,28 +1031,28 @@
         <v>2</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="I18" s="15">
         <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K18" s="14">
+        <v>-64.864864864864</v>
+      </c>
+      <c r="L18" s="14">
         <v>-61.764705882352</v>
       </c>
-      <c r="L18" s="14">
-        <v>-58.064516129032</v>
-      </c>
       <c r="M18" s="14">
-        <v>-64.864864864864</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.987654320987</v>
+        <v>-96.275071633237</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>57.142857142857</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="15">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H19" s="14">
-        <v>10.810810810810</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="I19" s="15">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J19" s="15">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="K19" s="14">
-        <v>5.223880597014</v>
+        <v>0.671140939597</v>
       </c>
       <c r="L19" s="14">
-        <v>-15.568862275449</v>
+        <v>-16.201117318435</v>
       </c>
       <c r="M19" s="14">
-        <v>-22.099447513812</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="N19" s="14">
-        <v>-73.040152963671</v>
+        <v>-73.166368515205</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1119,22 +1119,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L20" s="14">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="M20" s="14">
-        <v>233.333333333333</v>
+        <v>175</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.475138121547</v>
+        <v>-94.358974358974</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>41.666666666666</v>
+        <v>-30</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>5.454545454545</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I21" s="17">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="J21" s="17">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K21" s="18">
-        <v>4</v>
+        <v>0.909090909090</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.912547528517</v>
+        <v>-22.648083623693</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.066147859922</v>
+        <v>-20.143884892086</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.279742765273</v>
+        <v>-83.345836459114</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>125</v>
       </c>
       <c r="L22" s="14">
-        <v>-52.631578947368</v>
+        <v>-55</v>
       </c>
       <c r="M22" s="14">
         <v>-25</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-35</v>
+        <v>-12</v>
       </c>
       <c r="F24" s="15">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G24" s="15">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H24" s="14">
-        <v>-24.657534246575</v>
+        <v>-20.481927710843</v>
       </c>
       <c r="I24" s="15">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="J24" s="15">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.472324723247</v>
+        <v>-30.405405405405</v>
       </c>
       <c r="L24" s="14">
-        <v>-33.454545454545</v>
+        <v>-29.209621993127</v>
       </c>
       <c r="M24" s="14">
-        <v>-0.543478260869</v>
+        <v>8.421052631578</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14">
-        <v>-36.842105263157</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="15">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G25" s="15">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H25" s="14">
-        <v>-32.142857142857</v>
+        <v>-26.229508196721</v>
       </c>
       <c r="I25" s="15">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="J25" s="15">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.862745098039</v>
+        <v>-30.454545454545</v>
       </c>
       <c r="L25" s="14">
-        <v>-40.086206896551</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>-64</v>
+        <v>-75</v>
       </c>
       <c r="I26" s="15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J26" s="15">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K26" s="14">
-        <v>-2.127659574468</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="L26" s="14">
-        <v>-28.125</v>
+        <v>-26.153846153846</v>
       </c>
       <c r="M26" s="14">
-        <v>-24.590163934426</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F28" s="15">
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>-9.090909090909</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L28" s="14">
-        <v>-33.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,17 +1554,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
         <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-56</v>
       </c>
       <c r="M16" s="14">
-        <v>-37.5</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.285714285714</v>
+        <v>-94.021739130434</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="I17" s="15">
         <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="14">
-        <v>94.117647058823</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L17" s="14">
         <v>-19.512195121951</v>
       </c>
       <c r="M17" s="14">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N17" s="14">
-        <v>-35.294117647058</v>
+        <v>-37.735849056603</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
+        <v>4</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="15">
         <v>3</v>
       </c>
-      <c r="E18" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="15">
-        <v>2</v>
-      </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-81.818181818181</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K18" s="14">
-        <v>-64.864864864864</v>
+        <v>-63.414634146341</v>
       </c>
       <c r="L18" s="14">
-        <v>-61.764705882352</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="M18" s="14">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.275071633237</v>
+        <v>-95.934959349593</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G19" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H19" s="14">
-        <v>-15.909090909090</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="J19" s="15">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="K19" s="14">
-        <v>0.671140939597</v>
+        <v>-1.863354037267</v>
       </c>
       <c r="L19" s="14">
-        <v>-16.201117318435</v>
+        <v>-16.402116402116</v>
       </c>
       <c r="M19" s="14">
-        <v>-24.242424242424</v>
+        <v>-26.168224299065</v>
       </c>
       <c r="N19" s="14">
-        <v>-73.166368515205</v>
+        <v>-74.055829228243</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G20" s="15">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
       </c>
       <c r="I20" s="15">
         <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>120</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L20" s="14">
         <v>37.5</v>
       </c>
       <c r="M20" s="14">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.358974358974</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-30</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.523809523809</v>
+        <v>-30.136986301369</v>
       </c>
       <c r="I21" s="17">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="J21" s="17">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="K21" s="18">
-        <v>0.909090909090</v>
+        <v>-3.319502074688</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.648083623693</v>
+        <v>-23.606557377049</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.143884892086</v>
+        <v>-23.355263157894</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.345836459114</v>
+        <v>-83.683473389355</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1213,7 +1213,7 @@
         <v>-55</v>
       </c>
       <c r="M22" s="14">
-        <v>-25</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-12</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="15">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G24" s="15">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H24" s="14">
-        <v>-20.481927710843</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="I24" s="15">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="J24" s="15">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.405405405405</v>
+        <v>-31.25</v>
       </c>
       <c r="L24" s="14">
-        <v>-29.209621993127</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M24" s="14">
-        <v>8.421052631578</v>
+        <v>8.910891089108</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D25" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="14">
-        <v>-12.5</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F25" s="15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G25" s="15">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.229508196721</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="I25" s="15">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J25" s="15">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.454545454545</v>
+        <v>-30.801687763713</v>
       </c>
       <c r="L25" s="14">
-        <v>-37.037037037037</v>
+        <v>-36.923076923076</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
-      </c>
-      <c r="D26" s="15">
         <v>6</v>
       </c>
-      <c r="E26" s="14">
-        <v>-66.666666666666</v>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>-75</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I26" s="15">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J26" s="15">
         <v>53</v>
       </c>
       <c r="K26" s="14">
-        <v>-9.433962264150</v>
+        <v>1.886792452830</v>
       </c>
       <c r="L26" s="14">
-        <v>-26.153846153846</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M26" s="14">
-        <v>-23.809523809523</v>
+        <v>-23.943661971831</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I28" s="15">
         <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>-7.692307692307</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="14">
-        <v>-29.411764705882</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -940,37 +940,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>-15.384615384615</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L16" s="14">
-        <v>-56</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.619047619047</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.021739130434</v>
+        <v>-93.684210526315</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
         <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K17" s="14">
-        <v>83.333333333333</v>
+        <v>70</v>
       </c>
       <c r="L17" s="14">
-        <v>-19.512195121951</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M17" s="14">
-        <v>57.142857142857</v>
+        <v>47.826086956521</v>
       </c>
       <c r="N17" s="14">
-        <v>-37.735849056603</v>
+        <v>-38.181818181818</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15">
         <v>4</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="15">
-        <v>3</v>
       </c>
       <c r="G18" s="15">
         <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K18" s="14">
-        <v>-63.414634146341</v>
+        <v>-59.523809523809</v>
       </c>
       <c r="L18" s="14">
-        <v>-59.459459459459</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="M18" s="14">
-        <v>-62.5</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.934959349593</v>
+        <v>-95.641025641025</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F19" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G19" s="15">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H19" s="14">
-        <v>-27.083333333333</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="I19" s="15">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="J19" s="15">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.863354037267</v>
+        <v>-5.056179775280</v>
       </c>
       <c r="L19" s="14">
-        <v>-16.402116402116</v>
+        <v>-13.775510204081</v>
       </c>
       <c r="M19" s="14">
-        <v>-26.168224299065</v>
+        <v>-26.521739130434</v>
       </c>
       <c r="N19" s="14">
-        <v>-74.055829228243</v>
+        <v>-74.237804878048</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,28 +1104,28 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="15">
         <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="14">
         <v>37.5</v>
@@ -1134,7 +1134,7 @@
         <v>120</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.736842105263</v>
+        <v>-95.111111111111</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.136986301369</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="J21" s="17">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.319502074688</v>
+        <v>-5.703422053231</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.606557377049</v>
+        <v>-22.257053291536</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.355263157894</v>
+        <v>-23.456790123456</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.683473389355</v>
+        <v>-83.684210526315</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,35 +1185,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>4</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="15">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="L22" s="14">
-        <v>-55</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-35.714285714285</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.5</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G24" s="15">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H24" s="14">
-        <v>-24.444444444444</v>
+        <v>-21.686746987951</v>
       </c>
       <c r="I24" s="15">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="J24" s="15">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.25</v>
+        <v>-29.341317365269</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.571428571428</v>
+        <v>-27.384615384615</v>
       </c>
       <c r="M24" s="14">
-        <v>8.910891089108</v>
+        <v>11.320754716981</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-35.294117647058</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="15">
         <v>49</v>
       </c>
       <c r="G25" s="15">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H25" s="14">
-        <v>-24.615384615384</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="I25" s="15">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J25" s="15">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.801687763713</v>
+        <v>-28.455284552845</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.923076923076</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D26" s="15">
+        <v>7</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-71.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H26" s="14">
-        <v>-38.888888888888</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I26" s="15">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J26" s="15">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K26" s="14">
-        <v>1.886792452830</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>-18.181818181818</v>
+        <v>-21.126760563380</v>
       </c>
       <c r="M26" s="14">
-        <v>-23.943661971831</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1432,7 +1432,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
@@ -1441,22 +1441,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H28" s="14">
-        <v>-77.777777777777</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="I28" s="15">
         <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-14.285714285714</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L28" s="14">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1502,8 +1502,8 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1543,8 +1543,8 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1579,7 +1579,7 @@
         <v>-40</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-017pct.xlsx
+++ b/data/source/weekly/cs-en-us-017pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -946,31 +946,31 @@
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>-14.285714285714</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-57.142857142857</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-45.454545454545</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.684210526315</v>
+        <v>-93.658536585365</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G17" s="15">
         <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I17" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J17" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" s="14">
-        <v>70</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>-22.727272727272</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="M17" s="14">
-        <v>47.826086956521</v>
+        <v>40</v>
       </c>
       <c r="N17" s="14">
-        <v>-38.181818181818</v>
+        <v>-40.677966101694</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-66.666666666666</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="I18" s="15">
         <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K18" s="14">
-        <v>-59.523809523809</v>
+        <v>-65.306122448979</v>
       </c>
       <c r="L18" s="14">
-        <v>-55.263157894736</v>
+        <v>-57.5</v>
       </c>
       <c r="M18" s="14">
-        <v>-58.536585365853</v>
+        <v>-60.465116279069</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.641025641025</v>
+        <v>-95.873786407767</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>-41.176470588235</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G19" s="15">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H19" s="14">
-        <v>-25.490196078431</v>
+        <v>-28.070175438596</v>
       </c>
       <c r="I19" s="15">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="J19" s="15">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.056179775280</v>
+        <v>-4.188481675392</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.775510204081</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="M19" s="14">
-        <v>-26.521739130434</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="N19" s="14">
-        <v>-74.237804878048</v>
+        <v>-73.894436519258</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="M20" s="14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.111111111111</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.909090909090</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F21" s="17">
         <v>56</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.333333333333</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="I21" s="17">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="J21" s="17">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.703422053231</v>
+        <v>-7.342657342657</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.257053291536</v>
+        <v>-20.658682634730</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.456790123456</v>
+        <v>-22.965116279069</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.684210526315</v>
+        <v>-83.652066625539</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
-        <v>4</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="15">
         <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M22" s="14">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D24" s="15">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E24" s="14">
-        <v>28.571428571428</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F24" s="15">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G24" s="15">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H24" s="14">
-        <v>-21.686746987951</v>
+        <v>-32.941176470588</v>
       </c>
       <c r="I24" s="15">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="J24" s="15">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.341317365269</v>
+        <v>-32.303370786516</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.384615384615</v>
+        <v>-29.737609329446</v>
       </c>
       <c r="M24" s="14">
-        <v>11.320754716981</v>
+        <v>7.589285714285</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E25" s="14">
-        <v>33.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="15">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G25" s="15">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H25" s="14">
-        <v>-19.672131147541</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="I25" s="15">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J25" s="15">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="K25" s="14">
-        <v>-28.455284552845</v>
+        <v>-31.835205992509</v>
       </c>
       <c r="L25" s="14">
-        <v>-35.294117647058</v>
+        <v>-35.460992907801</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-71.428571428571</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G26" s="15">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>-45.454545454545</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="15">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J26" s="15">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K26" s="14">
-        <v>-6.666666666666</v>
+        <v>1.587301587301</v>
       </c>
       <c r="L26" s="14">
-        <v>-21.126760563380</v>
+        <v>-16.883116883116</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.333333333333</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>-81.818181818181</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K28" s="14">
-        <v>-29.411764705882</v>
+        <v>-35</v>
       </c>
       <c r="L28" s="14">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
@@ -1579,7 +1579,7 @@
         <v>-40</v>
       </c>
       <c r="L31" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
